--- a/Фото_площадок_задание_дизайнеру.xlsx
+++ b/Фото_площадок_задание_дизайнеру.xlsx
@@ -1159,7 +1159,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ул. Кирова, 12 (ЛиЛия)</t>
+          <t xml:space="preserve">ул. Кирова, 12</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ул. Кирова, 12 (ЛиЛия)</t>
+          <t xml:space="preserve">ул. Кирова, 12</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -4713,7 +4713,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ул. Кирова, 12 (ЛиЛия)</t>
+          <t xml:space="preserve">ул. Кирова, 12</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">

--- a/Фото_площадок_задание_дизайнеру.xlsx
+++ b/Фото_площадок_задание_дизайнеру.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L60"/>
+  <dimension ref="A1:L57"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -738,12 +738,12 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S5</t>
+          <t xml:space="preserve">S6</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ул. Замковая, 4 (часы МТС)</t>
+          <t xml:space="preserve">ул. Замковая, 19 (Универмаг)</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">обе</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -763,22 +763,22 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Динамический скроллер</t>
+          <t xml:space="preserve">Медиа-скроллер</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Общий план</t>
+          <t xml:space="preserve">Окружение</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Конструкция целиком, фронтально, чтобы читалась поверхность и было видно состояние</t>
+          <t xml:space="preserve">Встать у конструкции спиной к ней и снять место: остановка, вход в здание, пешеходный переход, поток людей. Горизонтальный кадр с высоты глаз, конструкция может попасть краем — она здесь не главная. Днём, в будни, когда есть люди и транспорт</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S5A.jpg</t>
+          <t xml:space="preserve">S6_env.jpg</t>
         </is>
       </c>
     </row>
@@ -790,12 +790,12 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S5</t>
+          <t xml:space="preserve">S7</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ул. Замковая, 4 (часы МТС)</t>
+          <t xml:space="preserve">ул. Замковая, 21 (м-н «Глобус»)</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Динамический скроллер</t>
+          <t xml:space="preserve">Медиа-скроллер</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -830,7 +830,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S5_env.jpg</t>
+          <t xml:space="preserve">S7_env.jpg</t>
         </is>
       </c>
     </row>
@@ -842,12 +842,12 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S5</t>
+          <t xml:space="preserve">S8</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ул. Замковая, 4 (часы МТС)</t>
+          <t xml:space="preserve">ул. Кирова, 3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -857,32 +857,32 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">B</t>
+          <t xml:space="preserve">обе</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Против хода движения пешеходов</t>
+          <t xml:space="preserve">По ходу движения потока</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Динамический скроллер</t>
+          <t xml:space="preserve">Статичный плакат</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Общий план</t>
+          <t xml:space="preserve">Окружение</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Конструкция целиком, фронтально, чтобы читалась поверхность и было видно состояние</t>
+          <t xml:space="preserve">Встать у конструкции спиной к ней и снять место: вход в магазин, парковка, остановка, люди и машины. Горизонтальный кадр с высоты глаз, конструкция может попасть краем — она здесь не главная. Днём, в будни, когда есть люди и транспорт</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S5B.jpg</t>
+          <t xml:space="preserve">S8_env.jpg</t>
         </is>
       </c>
     </row>
@@ -894,12 +894,12 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S6</t>
+          <t xml:space="preserve">S9</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ул. Замковая, 19 (Универмаг)</t>
+          <t xml:space="preserve">ул. Кирова, 4</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">По ходу движения пешеходов</t>
+          <t xml:space="preserve">По ходу движения потока</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Медиа-скроллер</t>
+          <t xml:space="preserve">Статичный плакат</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Встать у конструкции спиной к ней и снять место: остановка, вход в здание, пешеходный переход, поток людей. Горизонтальный кадр с высоты глаз, конструкция может попасть краем — она здесь не главная. Днём, в будни, когда есть люди и транспорт</t>
+          <t xml:space="preserve">Встать у конструкции спиной к ней и снять место: вход в магазин, парковка, остановка, люди и машины. Горизонтальный кадр с высоты глаз, конструкция может попасть краем — она здесь не главная. Днём, в будни, когда есть люди и транспорт</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S6_env.jpg</t>
+          <t xml:space="preserve">S9_env.jpg</t>
         </is>
       </c>
     </row>
@@ -946,12 +946,12 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S7</t>
+          <t xml:space="preserve">S10</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ул. Замковая, 21 (м-н «Глобус»)</t>
+          <t xml:space="preserve">ул. Кирова, 7</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -966,12 +966,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">По ходу движения пешеходов</t>
+          <t xml:space="preserve">По ходу движения потока</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Медиа-скроллер</t>
+          <t xml:space="preserve">Динамический скроллер</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Встать у конструкции спиной к ней и снять место: остановка, вход в здание, пешеходный переход, поток людей. Горизонтальный кадр с высоты глаз, конструкция может попасть краем — она здесь не главная. Днём, в будни, когда есть люди и транспорт</t>
+          <t xml:space="preserve">Встать у конструкции спиной к ней и снять место: вход в магазин, парковка, остановка, люди и машины. Горизонтальный кадр с высоты глаз, конструкция может попасть краем — она здесь не главная. Днём, в будни, когда есть люди и транспорт</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S7_env.jpg</t>
+          <t xml:space="preserve">S10_env.jpg</t>
         </is>
       </c>
     </row>
@@ -998,12 +998,12 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S8</t>
+          <t xml:space="preserve">S11</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ул. Кирова, 3</t>
+          <t xml:space="preserve">ул. Кирова, 12</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Статичный плакат</t>
+          <t xml:space="preserve">Динамический скроллер</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S8_env.jpg</t>
+          <t xml:space="preserve">S11_env.jpg</t>
         </is>
       </c>
     </row>
@@ -1050,12 +1050,12 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S9</t>
+          <t xml:space="preserve">S12</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ул. Кирова, 4</t>
+          <t xml:space="preserve">ул. Кирова, 13/19</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Статичный плакат</t>
+          <t xml:space="preserve">Динамический скроллер</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S9_env.jpg</t>
+          <t xml:space="preserve">S12_env.jpg</t>
         </is>
       </c>
     </row>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S10</t>
+          <t xml:space="preserve">S13</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ул. Кирова, 7</t>
+          <t xml:space="preserve">ул. Космонавтов, 11</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1142,7 +1142,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S10_env.jpg</t>
+          <t xml:space="preserve">S13_env.jpg</t>
         </is>
       </c>
     </row>
@@ -1154,12 +1154,12 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S11</t>
+          <t xml:space="preserve">S14</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ул. Кирова, 12</t>
+          <t xml:space="preserve">ул. Космонавтов, 12 (Автовокзал)</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1174,12 +1174,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">По ходу движения потока</t>
+          <t xml:space="preserve">По ходу движения пешеходов</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Динамический скроллер</t>
+          <t xml:space="preserve">Медиа-скроллер</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1189,12 +1189,12 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Встать у конструкции спиной к ней и снять место: вход в магазин, парковка, остановка, люди и машины. Горизонтальный кадр с высоты глаз, конструкция может попасть краем — она здесь не главная. Днём, в будни, когда есть люди и транспорт</t>
+          <t xml:space="preserve">Встать у конструкции спиной к ней и снять место: остановка, вход в здание, пешеходный переход, поток людей. Горизонтальный кадр с высоты глаз, конструкция может попасть краем — она здесь не главная. Днём, в будни, когда есть люди и транспорт</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S11_env.jpg</t>
+          <t xml:space="preserve">S14_env.jpg</t>
         </is>
       </c>
     </row>
@@ -1206,12 +1206,12 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S12</t>
+          <t xml:space="preserve">S15</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ул. Кирова, 13/19</t>
+          <t xml:space="preserve">ул. Ленина, 6 (Угол, Веста)</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1226,12 +1226,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">По ходу движения потока</t>
+          <t xml:space="preserve">По ходу движения пешеходов</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Динамический скроллер</t>
+          <t xml:space="preserve">Медиа-скроллер</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Встать у конструкции спиной к ней и снять место: вход в магазин, парковка, остановка, люди и машины. Горизонтальный кадр с высоты глаз, конструкция может попасть краем — она здесь не главная. Днём, в будни, когда есть люди и транспорт</t>
+          <t xml:space="preserve">Встать у конструкции спиной к ней и снять место: остановка, вход в здание, пешеходный переход, поток людей. Горизонтальный кадр с высоты глаз, конструкция может попасть краем — она здесь не главная. Днём, в будни, когда есть люди и транспорт</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S12_env.jpg</t>
+          <t xml:space="preserve">S15_env.jpg</t>
         </is>
       </c>
     </row>
@@ -1258,12 +1258,12 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S13</t>
+          <t xml:space="preserve">S16</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ул. Космонавтов, 11</t>
+          <t xml:space="preserve">ул. Ленина, 8</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Динамический скроллер</t>
+          <t xml:space="preserve">Статичный плакат</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S13_env.jpg</t>
+          <t xml:space="preserve">S16_env.jpg</t>
         </is>
       </c>
     </row>
@@ -1310,12 +1310,12 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S14</t>
+          <t xml:space="preserve">S17</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ул. Космонавтов, 12 (Автовокзал)</t>
+          <t xml:space="preserve">ул. Ленина, 16</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1330,12 +1330,12 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">По ходу движения пешеходов</t>
+          <t xml:space="preserve">По ходу движения потока</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Медиа-скроллер</t>
+          <t xml:space="preserve">Динамический скроллер</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1345,12 +1345,12 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Встать у конструкции спиной к ней и снять место: остановка, вход в здание, пешеходный переход, поток людей. Горизонтальный кадр с высоты глаз, конструкция может попасть краем — она здесь не главная. Днём, в будни, когда есть люди и транспорт</t>
+          <t xml:space="preserve">Встать у конструкции спиной к ней и снять место: вход в магазин, парковка, остановка, люди и машины. Горизонтальный кадр с высоты глаз, конструкция может попасть краем — она здесь не главная. Днём, в будни, когда есть люди и транспорт</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S14_env.jpg</t>
+          <t xml:space="preserve">S17_env.jpg</t>
         </is>
       </c>
     </row>
@@ -1362,12 +1362,12 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S15</t>
+          <t xml:space="preserve">S18</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ул. Ленина, 6 (Угол, Веста)</t>
+          <t xml:space="preserve">ул. Ленина, 19</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1382,12 +1382,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">По ходу движения пешеходов</t>
+          <t xml:space="preserve">По ходу движения потока</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Медиа-скроллер</t>
+          <t xml:space="preserve">Динамический скроллер</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1397,12 +1397,12 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Встать у конструкции спиной к ней и снять место: остановка, вход в здание, пешеходный переход, поток людей. Горизонтальный кадр с высоты глаз, конструкция может попасть краем — она здесь не главная. Днём, в будни, когда есть люди и транспорт</t>
+          <t xml:space="preserve">Встать у конструкции спиной к ней и снять место: вход в магазин, парковка, остановка, люди и машины. Горизонтальный кадр с высоты глаз, конструкция может попасть краем — она здесь не главная. Днём, в будни, когда есть люди и транспорт</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S15_env.jpg</t>
+          <t xml:space="preserve">S18_env.jpg</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S16</t>
+          <t xml:space="preserve">S19</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ул. Ленина, 8</t>
+          <t xml:space="preserve">Марко Сити_1 (ул. Ленина, 26А)</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Статичный плакат</t>
+          <t xml:space="preserve">Динамический скроллер</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S16_env.jpg</t>
+          <t xml:space="preserve">S19_env.jpg</t>
         </is>
       </c>
     </row>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S17</t>
+          <t xml:space="preserve">S20</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ул. Ленина, 16</t>
+          <t xml:space="preserve">Марко Сити_2 (ул. Ленина, 26А)</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S17_env.jpg</t>
+          <t xml:space="preserve">S20_env.jpg</t>
         </is>
       </c>
     </row>
@@ -1518,12 +1518,12 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S18</t>
+          <t xml:space="preserve">S21</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ул. Ленина, 19</t>
+          <t xml:space="preserve">Марко Сити_3 (ул. Ленина, 26А)</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1558,7 +1558,7 @@
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S18_env.jpg</t>
+          <t xml:space="preserve">S21_env.jpg</t>
         </is>
       </c>
     </row>
@@ -1570,12 +1570,12 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S19</t>
+          <t xml:space="preserve">S22</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Марко Сити_1 (ул. Ленина, 26А)</t>
+          <t xml:space="preserve">Марко Сити_4 (ул. Ленина, 26А)</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S19_env.jpg</t>
+          <t xml:space="preserve">S22_env.jpg</t>
         </is>
       </c>
     </row>
@@ -1622,12 +1622,12 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S20</t>
+          <t xml:space="preserve">S23</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Марко Сити_2 (ул. Ленина, 26А)</t>
+          <t xml:space="preserve">Марко Сити_5 (ул. Калинина, 2)</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S20_env.jpg</t>
+          <t xml:space="preserve">S23_env.jpg</t>
         </is>
       </c>
     </row>
@@ -1674,12 +1674,12 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S21</t>
+          <t xml:space="preserve">S24</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Марко Сити_3 (ул. Ленина, 26А)</t>
+          <t xml:space="preserve">ул. Ленина, 28 «Синий» дом</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Динамический скроллер</t>
+          <t xml:space="preserve">Медиа-скроллер</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S21_env.jpg</t>
+          <t xml:space="preserve">S24_env.jpg</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S22</t>
+          <t xml:space="preserve">S25</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Марко Сити_4 (ул. Ленина, 26А)</t>
+          <t xml:space="preserve">ул. Ленина, 35, ТЦ «Пассаж»</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1751,7 +1751,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Динамический скроллер</t>
+          <t xml:space="preserve">Статичный плакат</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S22_env.jpg</t>
+          <t xml:space="preserve">S25_env.jpg</t>
         </is>
       </c>
     </row>
@@ -1778,12 +1778,12 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S23</t>
+          <t xml:space="preserve">S26</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Марко Сити_5 (ул. Калинина, 2)</t>
+          <t xml:space="preserve">ул. Ленина, 53 (Белла Мария)</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Динамический скроллер</t>
+          <t xml:space="preserve">Статичный плакат</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1818,7 +1818,7 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S23_env.jpg</t>
+          <t xml:space="preserve">S26_env.jpg</t>
         </is>
       </c>
     </row>
@@ -1830,12 +1830,12 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S24</t>
+          <t xml:space="preserve">S27</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ул. Ленина, 28 «Синий» дом</t>
+          <t xml:space="preserve">Пересечение ул. Коммунистической и ул. Горовца</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Медиа-скроллер</t>
+          <t xml:space="preserve">Статичный плакат</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -1870,7 +1870,7 @@
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S24_env.jpg</t>
+          <t xml:space="preserve">S27_env.jpg</t>
         </is>
       </c>
     </row>
@@ -1882,12 +1882,12 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S25</t>
+          <t xml:space="preserve">S28</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ул. Ленина, 35, ТЦ «Пассаж»</t>
+          <t xml:space="preserve">пр-т Московский, 9, к. 1</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">По ходу движения потока</t>
+          <t xml:space="preserve">По ходу движения транспорта</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Встать у конструкции спиной к ней и снять место: вход в магазин, парковка, остановка, люди и машины. Горизонтальный кадр с высоты глаз, конструкция может попасть краем — она здесь не главная. Днём, в будни, когда есть люди и транспорт</t>
+          <t xml:space="preserve">Встать у конструкции спиной к ней и снять место: перекрёсток, полосы движения, машины в кадре. Горизонтальный кадр с высоты глаз, конструкция может попасть краем — она здесь не главная. Днём, в будни, когда есть люди и транспорт</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S25_env.jpg</t>
+          <t xml:space="preserve">S28_env.jpg</t>
         </is>
       </c>
     </row>
@@ -1934,12 +1934,12 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S26</t>
+          <t xml:space="preserve">S29</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ул. Ленина, 53 (Белла Мария)</t>
+          <t xml:space="preserve">Московский пр-т, 10 (Почта)</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -1954,12 +1954,12 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">По ходу движения потока</t>
+          <t xml:space="preserve">По ходу движения транспорта</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Статичный плакат</t>
+          <t xml:space="preserve">Медиа-скроллер</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -1969,12 +1969,12 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Встать у конструкции спиной к ней и снять место: вход в магазин, парковка, остановка, люди и машины. Горизонтальный кадр с высоты глаз, конструкция может попасть краем — она здесь не главная. Днём, в будни, когда есть люди и транспорт</t>
+          <t xml:space="preserve">Встать у конструкции спиной к ней и снять место: перекрёсток, полосы движения, машины в кадре. Горизонтальный кадр с высоты глаз, конструкция может попасть краем — она здесь не главная. Днём, в будни, когда есть люди и транспорт</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S26_env.jpg</t>
+          <t xml:space="preserve">S29_env.jpg</t>
         </is>
       </c>
     </row>
@@ -1986,12 +1986,12 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S27</t>
+          <t xml:space="preserve">S30</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Пересечение ул. Коммунистической и ул. Горовца</t>
+          <t xml:space="preserve">Московский пр-т, 16</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -2006,12 +2006,12 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">По ходу движения потока</t>
+          <t xml:space="preserve">По ходу движения транспорта</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Статичный плакат</t>
+          <t xml:space="preserve">Динамический скроллер</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2021,12 +2021,12 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Встать у конструкции спиной к ней и снять место: вход в магазин, парковка, остановка, люди и машины. Горизонтальный кадр с высоты глаз, конструкция может попасть краем — она здесь не главная. Днём, в будни, когда есть люди и транспорт</t>
+          <t xml:space="preserve">Встать у конструкции спиной к ней и снять место: перекрёсток, полосы движения, машины в кадре. Горизонтальный кадр с высоты глаз, конструкция может попасть краем — она здесь не главная. Днём, в будни, когда есть люди и транспорт</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S27_env.jpg</t>
+          <t xml:space="preserve">S30_env.jpg</t>
         </is>
       </c>
     </row>
@@ -2038,12 +2038,12 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S28</t>
+          <t xml:space="preserve">S31</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">пр-т Московский, 9, к. 1</t>
+          <t xml:space="preserve">пр-т Московский, 17/1 (школа № 31)</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -2078,7 +2078,7 @@
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S28_env.jpg</t>
+          <t xml:space="preserve">S31_env.jpg</t>
         </is>
       </c>
     </row>
@@ -2090,12 +2090,12 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S29</t>
+          <t xml:space="preserve">S32</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Московский пр-т, 10 (Почта)</t>
+          <t xml:space="preserve">Московский пр-т, 30 (м-н «Витебские продукты»)</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Медиа-скроллер</t>
+          <t xml:space="preserve">Динамический скроллер</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S29_env.jpg</t>
+          <t xml:space="preserve">S32_env.jpg</t>
         </is>
       </c>
     </row>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S30</t>
+          <t xml:space="preserve">S33</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Московский пр-т, 16</t>
+          <t xml:space="preserve">Победы пр-т / Московский пр-т, 33 (Педуниверситет)</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -2167,7 +2167,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Динамический скроллер</t>
+          <t xml:space="preserve">Статичный плакат</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2182,7 +2182,7 @@
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S30_env.jpg</t>
+          <t xml:space="preserve">S33_env.jpg</t>
         </is>
       </c>
     </row>
@@ -2194,12 +2194,12 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S31</t>
+          <t xml:space="preserve">S34</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">пр-т Московский, 17/1 (школа № 31)</t>
+          <t xml:space="preserve">Московский пр-т, 35 (м-н «Астраханский»)</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2219,7 +2219,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Статичный плакат</t>
+          <t xml:space="preserve">Динамический скроллер</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S31_env.jpg</t>
+          <t xml:space="preserve">S34_env.jpg</t>
         </is>
       </c>
     </row>
@@ -2246,12 +2246,12 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S32</t>
+          <t xml:space="preserve">S35</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Московский пр-т, 30 (м-н «Витебские продукты»)</t>
+          <t xml:space="preserve">Московский пр-т, 60 (м-н «Евроопт»)</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S32_env.jpg</t>
+          <t xml:space="preserve">S35_env.jpg</t>
         </is>
       </c>
     </row>
@@ -2298,12 +2298,12 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S33</t>
+          <t xml:space="preserve">S36</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Победы пр-т / Московский пр-т, 33 (Педуниверситет)</t>
+          <t xml:space="preserve">Московский пр-т, 68 (перекрёсток Машерова)</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -2338,7 +2338,7 @@
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S33_env.jpg</t>
+          <t xml:space="preserve">S36_env.jpg</t>
         </is>
       </c>
     </row>
@@ -2350,12 +2350,12 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S34</t>
+          <t xml:space="preserve">S37</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Московский пр-т, 35 (м-н «Астраханский»)</t>
+          <t xml:space="preserve">Московский пр-т, 86 (МакДональдс)</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S34_env.jpg</t>
+          <t xml:space="preserve">S37_env.jpg</t>
         </is>
       </c>
     </row>
@@ -2402,12 +2402,12 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S35</t>
+          <t xml:space="preserve">S38</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Московский пр-т, 60 (м-н «Евроопт»)</t>
+          <t xml:space="preserve">Перекрёсток пр-та Строителей и пр-та Черняховского</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -2427,7 +2427,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Динамический скроллер</t>
+          <t xml:space="preserve">Статичный плакат</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S35_env.jpg</t>
+          <t xml:space="preserve">S38_env.jpg</t>
         </is>
       </c>
     </row>
@@ -2454,12 +2454,12 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S36</t>
+          <t xml:space="preserve">S39</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Московский пр-т, 68 (перекрёсток Машерова)</t>
+          <t xml:space="preserve">Строителей пр-т, 1 (Континент-1)</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -2474,12 +2474,12 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">По ходу движения транспорта</t>
+          <t xml:space="preserve">По ходу движения потока</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Статичный плакат</t>
+          <t xml:space="preserve">Динамический скроллер</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -2489,12 +2489,12 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Встать у конструкции спиной к ней и снять место: перекрёсток, полосы движения, машины в кадре. Горизонтальный кадр с высоты глаз, конструкция может попасть краем — она здесь не главная. Днём, в будни, когда есть люди и транспорт</t>
+          <t xml:space="preserve">Встать у конструкции спиной к ней и снять место: вход в магазин, парковка, остановка, люди и машины. Горизонтальный кадр с высоты глаз, конструкция может попасть краем — она здесь не главная. Днём, в будни, когда есть люди и транспорт</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S36_env.jpg</t>
+          <t xml:space="preserve">S39_env.jpg</t>
         </is>
       </c>
     </row>
@@ -2506,12 +2506,12 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S37</t>
+          <t xml:space="preserve">S40</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Московский пр-т, 86 (МакДональдс)</t>
+          <t xml:space="preserve">Строителей пр-т, 1 (Континент-2)</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">По ходу движения транспорта</t>
+          <t xml:space="preserve">По ходу движения потока</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -2541,12 +2541,12 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Встать у конструкции спиной к ней и снять место: перекрёсток, полосы движения, машины в кадре. Горизонтальный кадр с высоты глаз, конструкция может попасть краем — она здесь не главная. Днём, в будни, когда есть люди и транспорт</t>
+          <t xml:space="preserve">Встать у конструкции спиной к ней и снять место: вход в магазин, парковка, остановка, люди и машины. Горизонтальный кадр с высоты глаз, конструкция может попасть краем — она здесь не главная. Днём, в будни, когда есть люди и транспорт</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S37_env.jpg</t>
+          <t xml:space="preserve">S40_env.jpg</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S38</t>
+          <t xml:space="preserve">S41</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Перекрёсток пр-та Строителей и пр-та Черняховского</t>
+          <t xml:space="preserve">Строителей пр-т, 8к2 — ул. Чкалова (офис МТС)</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -2578,7 +2578,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">По ходу движения транспорта</t>
+          <t xml:space="preserve">По ходу движения потока</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Встать у конструкции спиной к ней и снять место: перекрёсток, полосы движения, машины в кадре. Горизонтальный кадр с высоты глаз, конструкция может попасть краем — она здесь не главная. Днём, в будни, когда есть люди и транспорт</t>
+          <t xml:space="preserve">Встать у конструкции спиной к ней и снять место: вход в магазин, парковка, остановка, люди и машины. Горизонтальный кадр с высоты глаз, конструкция может попасть краем — она здесь не главная. Днём, в будни, когда есть люди и транспорт</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S38_env.jpg</t>
+          <t xml:space="preserve">S41_env.jpg</t>
         </is>
       </c>
     </row>
@@ -2610,12 +2610,12 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S39</t>
+          <t xml:space="preserve">S42</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Строителей пр-т, 1 (Континент-1)</t>
+          <t xml:space="preserve">Строителей пр-т, 9 «Бригантина»</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -2635,7 +2635,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Динамический скроллер</t>
+          <t xml:space="preserve">Статичный плакат</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -2650,7 +2650,7 @@
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S39_env.jpg</t>
+          <t xml:space="preserve">S42_env.jpg</t>
         </is>
       </c>
     </row>
@@ -2662,12 +2662,12 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S40</t>
+          <t xml:space="preserve">S43</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Строителей пр-т, 1 (Континент-2)</t>
+          <t xml:space="preserve">Строителей пр-т, 15В (ТЦ «ТРИО»)</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Динамический скроллер</t>
+          <t xml:space="preserve">Медиа-скроллер</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S40_env.jpg</t>
+          <t xml:space="preserve">S43_env.jpg</t>
         </is>
       </c>
     </row>
@@ -2714,12 +2714,12 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S41</t>
+          <t xml:space="preserve">S44</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Строителей пр-т, 8к2 — ул. Чкалова (офис МТС)</t>
+          <t xml:space="preserve">Строителей пр-т, 15В (ТЦ «ТРИО-2»)</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Статичный плакат</t>
+          <t xml:space="preserve">Динамический скроллер</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S41_env.jpg</t>
+          <t xml:space="preserve">S44_env.jpg</t>
         </is>
       </c>
     </row>
@@ -2766,12 +2766,12 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S42</t>
+          <t xml:space="preserve">S45</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Строителей пр-т, 9 «Бригантина»</t>
+          <t xml:space="preserve">Черняховского пр-т, 3</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -2786,12 +2786,12 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">По ходу движения потока</t>
+          <t xml:space="preserve">По ходу движения транспорта</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Статичный плакат</t>
+          <t xml:space="preserve">Динамический скроллер</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -2801,12 +2801,12 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Встать у конструкции спиной к ней и снять место: вход в магазин, парковка, остановка, люди и машины. Горизонтальный кадр с высоты глаз, конструкция может попасть краем — она здесь не главная. Днём, в будни, когда есть люди и транспорт</t>
+          <t xml:space="preserve">Встать у конструкции спиной к ней и снять место: перекрёсток, полосы движения, машины в кадре. Горизонтальный кадр с высоты глаз, конструкция может попасть краем — она здесь не главная. Днём, в будни, когда есть люди и транспорт</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S42_env.jpg</t>
+          <t xml:space="preserve">S45_env.jpg</t>
         </is>
       </c>
     </row>
@@ -2818,12 +2818,12 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S43</t>
+          <t xml:space="preserve">S46</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Строителей пр-т, 15В (ТЦ «ТРИО»)</t>
+          <t xml:space="preserve">ул. Чкалова (ТД «Омега»)</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Медиа-скроллер</t>
+          <t xml:space="preserve">Статичный плакат</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S43_env.jpg</t>
+          <t xml:space="preserve">S46_env.jpg</t>
         </is>
       </c>
     </row>
@@ -2870,12 +2870,12 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S44</t>
+          <t xml:space="preserve">S47</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Строителей пр-т, 15В (ТЦ «ТРИО-2»)</t>
+          <t xml:space="preserve">пр-т Фрунзе, 16</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Динамический скроллер</t>
+          <t xml:space="preserve">Статичный плакат</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S44_env.jpg</t>
+          <t xml:space="preserve">S47_env.jpg</t>
         </is>
       </c>
     </row>
@@ -2922,12 +2922,12 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S45</t>
+          <t xml:space="preserve">S48</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Черняховского пр-т, 3</t>
+          <t xml:space="preserve">ул. Фрунзе, 46 («Зелена Гура»)</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -2942,7 +2942,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">По ходу движения транспорта</t>
+          <t xml:space="preserve">По ходу движения потока</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -2957,12 +2957,12 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Встать у конструкции спиной к ней и снять место: перекрёсток, полосы движения, машины в кадре. Горизонтальный кадр с высоты глаз, конструкция может попасть краем — она здесь не главная. Днём, в будни, когда есть люди и транспорт</t>
+          <t xml:space="preserve">Встать у конструкции спиной к ней и снять место: вход в магазин, парковка, остановка, люди и машины. Горизонтальный кадр с высоты глаз, конструкция может попасть краем — она здесь не главная. Днём, в будни, когда есть люди и транспорт</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S45_env.jpg</t>
+          <t xml:space="preserve">S48_env.jpg</t>
         </is>
       </c>
     </row>
@@ -2974,12 +2974,12 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S46</t>
+          <t xml:space="preserve">S49</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ул. Чкалова (ТД «Омега»)</t>
+          <t xml:space="preserve">Перекрёсток пр-та Фрунзе и ул. Смоленской</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">По ходу движения потока</t>
+          <t xml:space="preserve">По ходу движения транспорта</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -3009,12 +3009,12 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Встать у конструкции спиной к ней и снять место: вход в магазин, парковка, остановка, люди и машины. Горизонтальный кадр с высоты глаз, конструкция может попасть краем — она здесь не главная. Днём, в будни, когда есть люди и транспорт</t>
+          <t xml:space="preserve">Встать у конструкции спиной к ней и снять место: перекрёсток, полосы движения, машины в кадре. Горизонтальный кадр с высоты глаз, конструкция может попасть краем — она здесь не главная. Днём, в будни, когда есть люди и транспорт</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S46_env.jpg</t>
+          <t xml:space="preserve">S49_env.jpg</t>
         </is>
       </c>
     </row>
@@ -3026,17 +3026,17 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S47</t>
+          <t xml:space="preserve">S50</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">пр-т Фрунзе, 16</t>
+          <t xml:space="preserve">г. Полоцк, ул. Гоголя (Дом торговли)</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Витебск</t>
+          <t xml:space="preserve">Полоцк</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -3066,7 +3066,7 @@
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S47_env.jpg</t>
+          <t xml:space="preserve">S50_env.jpg</t>
         </is>
       </c>
     </row>
@@ -3078,17 +3078,17 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S48</t>
+          <t xml:space="preserve">S51</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ул. Фрунзе, 46 («Зелена Гура»)</t>
+          <t xml:space="preserve">г. Полоцк, ул. Октябрьская (ТЦ «Дионис»)</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Витебск</t>
+          <t xml:space="preserve">Полоцк</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Динамический скроллер</t>
+          <t xml:space="preserve">Статичный плакат</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -3118,7 +3118,7 @@
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S48_env.jpg</t>
+          <t xml:space="preserve">S51_env.jpg</t>
         </is>
       </c>
     </row>
@@ -3130,17 +3130,17 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S49</t>
+          <t xml:space="preserve">S52</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Перекрёсток пр-та Фрунзе и ул. Смоленской</t>
+          <t xml:space="preserve">г. Полоцк, ул. Юбилейная, д. 7Б</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Витебск</t>
+          <t xml:space="preserve">Полоцк</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">По ходу движения транспорта</t>
+          <t xml:space="preserve">По ходу движения потока</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Встать у конструкции спиной к ней и снять место: перекрёсток, полосы движения, машины в кадре. Горизонтальный кадр с высоты глаз, конструкция может попасть краем — она здесь не главная. Днём, в будни, когда есть люди и транспорт</t>
+          <t xml:space="preserve">Встать у конструкции спиной к ней и снять место: вход в магазин, парковка, остановка, люди и машины. Горизонтальный кадр с высоты глаз, конструкция может попасть краем — она здесь не главная. Днём, в будни, когда есть люди и транспорт</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S49_env.jpg</t>
+          <t xml:space="preserve">S52_env.jpg</t>
         </is>
       </c>
     </row>
@@ -3182,17 +3182,17 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S50</t>
+          <t xml:space="preserve">LED-1</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">г. Полоцк, ул. Гоголя (Дом торговли)</t>
+          <t xml:space="preserve">LED-экран 6×3, Ленина 26А (ТЦ «Марко-Сити»)</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Полоцк</t>
+          <t xml:space="preserve">Витебск</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -3202,27 +3202,27 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">По ходу движения потока</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Статичный плакат</t>
+          <t xml:space="preserve">LED-экран 6×3</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Окружение</t>
+          <t xml:space="preserve">Общий план</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Встать у конструкции спиной к ней и снять место: вход в магазин, парковка, остановка, люди и машины. Горизонтальный кадр с высоты глаз, конструкция может попасть краем — она здесь не главная. Днём, в будни, когда есть люди и транспорт</t>
+          <t xml:space="preserve">Конструкция целиком, фронтально, чтобы читалась поверхность и было видно состояние</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S50_env.jpg</t>
+          <t xml:space="preserve">LED-1.jpg</t>
         </is>
       </c>
     </row>
@@ -3234,17 +3234,17 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S51</t>
+          <t xml:space="preserve">LED-1</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">г. Полоцк, ул. Октябрьская (ТЦ «Дионис»)</t>
+          <t xml:space="preserve">LED-экран 6×3, Ленина 26А (ТЦ «Марко-Сити»)</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Полоцк</t>
+          <t xml:space="preserve">Витебск</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">По ходу движения потока</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Статичный плакат</t>
+          <t xml:space="preserve">LED-экран 6×3</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Встать у конструкции спиной к ней и снять место: вход в магазин, парковка, остановка, люди и машины. Горизонтальный кадр с высоты глаз, конструкция может попасть краем — она здесь не главная. Днём, в будни, когда есть люди и транспорт</t>
+          <t xml:space="preserve">Встать у конструкции спиной к ней и снять место: перекрёсток, полосы движения, машины в кадре. Горизонтальный кадр с высоты глаз, конструкция может попасть краем — она здесь не главная. Днём, в будни, когда есть люди и транспорт</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S51_env.jpg</t>
+          <t xml:space="preserve">LED-1_env.jpg</t>
         </is>
       </c>
     </row>
@@ -3286,17 +3286,17 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S52</t>
+          <t xml:space="preserve">LED-2</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">г. Полоцк, ул. Юбилейная, д. 7Б</t>
+          <t xml:space="preserve">LED-экран 6×3, Московский 60 (Евроопт)</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Полоцк</t>
+          <t xml:space="preserve">Витебск</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -3306,27 +3306,27 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">По ходу движения потока</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Статичный плакат</t>
+          <t xml:space="preserve">LED-экран 6×3</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Окружение</t>
+          <t xml:space="preserve">Общий план</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Встать у конструкции спиной к ней и снять место: вход в магазин, парковка, остановка, люди и машины. Горизонтальный кадр с высоты глаз, конструкция может попасть краем — она здесь не главная. Днём, в будни, когда есть люди и транспорт</t>
+          <t xml:space="preserve">Конструкция целиком, фронтально, чтобы читалась поверхность и было видно состояние</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S52_env.jpg</t>
+          <t xml:space="preserve">LED-2.jpg</t>
         </is>
       </c>
     </row>
@@ -3338,12 +3338,12 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">LED-1</t>
+          <t xml:space="preserve">LED-2</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">LED-экран 6×3, Ленина 26А (ТЦ «Марко-Сити»)</t>
+          <t xml:space="preserve">LED-экран 6×3, Московский 60 (Евроопт)</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -3368,184 +3368,28 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Общий план</t>
+          <t xml:space="preserve">Окружение</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Конструкция целиком, фронтально, чтобы читалась поверхность и было видно состояние</t>
+          <t xml:space="preserve">Встать у конструкции спиной к ней и снять место: перекрёсток, полосы движения, машины в кадре. Горизонтальный кадр с высоты глаз, конструкция может попасть краем — она здесь не главная. Днём, в будни, когда есть люди и транспорт</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">LED-1.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">56</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LED-1</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LED-экран 6×3, Ленина 26А (ТЦ «Марко-Сити»)</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Витебск</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">обе</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LED-экран 6×3</t>
-        </is>
-      </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Окружение</t>
-        </is>
-      </c>
-      <c r="I58" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Встать у конструкции спиной к ней и снять место: перекрёсток, полосы движения, машины в кадре. Горизонтальный кадр с высоты глаз, конструкция может попасть краем — она здесь не главная. Днём, в будни, когда есть люди и транспорт</t>
-        </is>
-      </c>
-      <c r="J58" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LED-1_env.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">57</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LED-2</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LED-экран 6×3, Московский 60 (Евроопт)</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Витебск</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">обе</t>
-        </is>
-      </c>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="G59" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LED-экран 6×3</t>
-        </is>
-      </c>
-      <c r="H59" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Общий план</t>
-        </is>
-      </c>
-      <c r="I59" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Конструкция целиком, фронтально, чтобы читалась поверхность и было видно состояние</t>
-        </is>
-      </c>
-      <c r="J59" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LED-2.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">58</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LED-2</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LED-экран 6×3, Московский 60 (Евроопт)</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Витебск</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">обе</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="G60" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LED-экран 6×3</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Окружение</t>
-        </is>
-      </c>
-      <c r="I60" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Встать у конструкции спиной к ней и снять место: перекрёсток, полосы движения, машины в кадре. Горизонтальный кадр с высоты глаз, конструкция может попасть краем — она здесь не главная. Днём, в будни, когда есть люди и транспорт</t>
-        </is>
-      </c>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
           <t xml:space="preserve">LED-2_env.jpg</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L60"/>
+  <autoFilter ref="A1:L57"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J107"/>
+  <dimension ref="A1:J105"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -4032,12 +3876,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S5</t>
+          <t xml:space="preserve">S6</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ул. Замковая, 4 (часы МТС)</t>
+          <t xml:space="preserve">ул. Замковая, 19 (Универмаг)</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -4057,17 +3901,17 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Динамический скроллер</t>
+          <t xml:space="preserve">Медиа-скроллер</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">нужно снять</t>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">есть</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
@@ -4077,19 +3921,19 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S5</t>
+          <t xml:space="preserve">S6</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ул. Замковая, 4 (часы МТС)</t>
+          <t xml:space="preserve">ул. Замковая, 19 (Универмаг)</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -4114,12 +3958,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">нужно снять</t>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">есть</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -4129,19 +3973,19 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S6</t>
+          <t xml:space="preserve">S7</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ул. Замковая, 19 (Универмаг)</t>
+          <t xml:space="preserve">ул. Замковая, 21 (м-н «Глобус»)</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -4188,12 +4032,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S6</t>
+          <t xml:space="preserve">S7</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ул. Замковая, 19 (Универмаг)</t>
+          <t xml:space="preserve">ул. Замковая, 21 (м-н «Глобус»)</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -4218,7 +4062,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
@@ -4240,12 +4084,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S7</t>
+          <t xml:space="preserve">S8</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ул. Замковая, 21 (м-н «Глобус»)</t>
+          <t xml:space="preserve">ул. Кирова, 3</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -4260,17 +4104,17 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">По ходу движения пешеходов</t>
+          <t xml:space="preserve">По ходу движения потока</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Медиа-скроллер</t>
+          <t xml:space="preserve">Статичный плакат</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
@@ -4292,12 +4136,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S7</t>
+          <t xml:space="preserve">S8</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ул. Замковая, 21 (м-н «Глобус»)</t>
+          <t xml:space="preserve">ул. Кирова, 3</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -4312,17 +4156,17 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Против хода движения пешеходов</t>
+          <t xml:space="preserve">Против хода движения потока</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Динамический скроллер</t>
+          <t xml:space="preserve">Статичный плакат</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
@@ -4344,12 +4188,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S8</t>
+          <t xml:space="preserve">S9</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ул. Кирова, 3</t>
+          <t xml:space="preserve">ул. Кирова, 4</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -4374,7 +4218,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
@@ -4396,12 +4240,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S8</t>
+          <t xml:space="preserve">S9</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ул. Кирова, 3</t>
+          <t xml:space="preserve">ул. Кирова, 4</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -4448,12 +4292,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S9</t>
+          <t xml:space="preserve">S10</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ул. Кирова, 4</t>
+          <t xml:space="preserve">ул. Кирова, 7</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -4473,12 +4317,12 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Статичный плакат</t>
+          <t xml:space="preserve">Динамический скроллер</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
@@ -4500,12 +4344,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S9</t>
+          <t xml:space="preserve">S10</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ул. Кирова, 4</t>
+          <t xml:space="preserve">ул. Кирова, 7</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -4552,12 +4396,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S10</t>
+          <t xml:space="preserve">S11</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ул. Кирова, 7</t>
+          <t xml:space="preserve">ул. Кирова, 12</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -4604,12 +4448,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S10</t>
+          <t xml:space="preserve">S11</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ул. Кирова, 7</t>
+          <t xml:space="preserve">ул. Кирова, 12</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -4629,12 +4473,12 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Статичный плакат</t>
+          <t xml:space="preserve">Динамический скроллер</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
@@ -4656,12 +4500,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S11</t>
+          <t xml:space="preserve">S12</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ул. Кирова, 12</t>
+          <t xml:space="preserve">ул. Кирова, 13/19</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -4686,7 +4530,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
@@ -4708,12 +4552,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S11</t>
+          <t xml:space="preserve">S12</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ул. Кирова, 12</t>
+          <t xml:space="preserve">ул. Кирова, 13/19</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -4733,12 +4577,12 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Динамический скроллер</t>
+          <t xml:space="preserve">Статичный плакат</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
@@ -4760,12 +4604,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S12</t>
+          <t xml:space="preserve">S13</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ул. Кирова, 13/19</t>
+          <t xml:space="preserve">ул. Космонавтов, 11</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -4790,7 +4634,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
@@ -4812,12 +4656,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S12</t>
+          <t xml:space="preserve">S13</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ул. Кирова, 13/19</t>
+          <t xml:space="preserve">ул. Космонавтов, 11</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -4837,12 +4681,12 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Статичный плакат</t>
+          <t xml:space="preserve">Динамический скроллер</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
@@ -4864,12 +4708,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S13</t>
+          <t xml:space="preserve">S14</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ул. Космонавтов, 11</t>
+          <t xml:space="preserve">ул. Космонавтов, 12 (Автовокзал)</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -4884,17 +4728,17 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">По ходу движения потока</t>
+          <t xml:space="preserve">По ходу движения пешеходов</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Динамический скроллер</t>
+          <t xml:space="preserve">Медиа-скроллер</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
@@ -4916,12 +4760,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S13</t>
+          <t xml:space="preserve">S14</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ул. Космонавтов, 11</t>
+          <t xml:space="preserve">ул. Космонавтов, 12 (Автовокзал)</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -4936,17 +4780,17 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Против хода движения потока</t>
+          <t xml:space="preserve">Против хода движения пешеходов</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Динамический скроллер</t>
+          <t xml:space="preserve">Медиа-скроллер</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
@@ -4968,12 +4812,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S14</t>
+          <t xml:space="preserve">S15</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ул. Космонавтов, 12 (Автовокзал)</t>
+          <t xml:space="preserve">ул. Ленина, 6 (Угол, Веста)</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -4998,7 +4842,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
@@ -5020,12 +4864,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S14</t>
+          <t xml:space="preserve">S15</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ул. Космонавтов, 12 (Автовокзал)</t>
+          <t xml:space="preserve">ул. Ленина, 6 (Угол, Веста)</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -5045,12 +4889,12 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Медиа-скроллер</t>
+          <t xml:space="preserve">Динамический скроллер</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
@@ -5072,12 +4916,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S15</t>
+          <t xml:space="preserve">S16</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ул. Ленина, 6 (Угол, Веста)</t>
+          <t xml:space="preserve">ул. Ленина, 8</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -5092,17 +4936,17 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">По ходу движения пешеходов</t>
+          <t xml:space="preserve">По ходу движения потока</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Медиа-скроллер</t>
+          <t xml:space="preserve">Статичный плакат</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
@@ -5124,12 +4968,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S15</t>
+          <t xml:space="preserve">S16</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ул. Ленина, 6 (Угол, Веста)</t>
+          <t xml:space="preserve">ул. Ленина, 8</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -5144,17 +4988,17 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Против хода движения пешеходов</t>
+          <t xml:space="preserve">Против хода движения потока</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Динамический скроллер</t>
+          <t xml:space="preserve">Статичный плакат</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
@@ -5176,12 +5020,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S16</t>
+          <t xml:space="preserve">S17</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ул. Ленина, 8</t>
+          <t xml:space="preserve">ул. Ленина, 16</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -5201,12 +5045,12 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Статичный плакат</t>
+          <t xml:space="preserve">Динамический скроллер</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
@@ -5228,12 +5072,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S16</t>
+          <t xml:space="preserve">S17</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ул. Ленина, 8</t>
+          <t xml:space="preserve">ул. Ленина, 16</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -5253,12 +5097,12 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Статичный плакат</t>
+          <t xml:space="preserve">Динамический скроллер</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
@@ -5280,12 +5124,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S17</t>
+          <t xml:space="preserve">S18</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ул. Ленина, 16</t>
+          <t xml:space="preserve">ул. Ленина, 19</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -5332,12 +5176,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S17</t>
+          <t xml:space="preserve">S18</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ул. Ленина, 16</t>
+          <t xml:space="preserve">ул. Ленина, 19</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -5362,7 +5206,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
@@ -5384,12 +5228,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S18</t>
+          <t xml:space="preserve">S19</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ул. Ленина, 19</t>
+          <t xml:space="preserve">Марко Сити_1 (ул. Ленина, 26А)</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -5414,7 +5258,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
@@ -5436,12 +5280,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S18</t>
+          <t xml:space="preserve">S19</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ул. Ленина, 19</t>
+          <t xml:space="preserve">Марко Сити_1 (ул. Ленина, 26А)</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -5466,7 +5310,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
@@ -5488,12 +5332,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S19</t>
+          <t xml:space="preserve">S20</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Марко Сити_1 (ул. Ленина, 26А)</t>
+          <t xml:space="preserve">Марко Сити_2 (ул. Ленина, 26А)</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -5518,7 +5362,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr">
@@ -5540,12 +5384,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S19</t>
+          <t xml:space="preserve">S20</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Марко Сити_1 (ул. Ленина, 26А)</t>
+          <t xml:space="preserve">Марко Сити_2 (ул. Ленина, 26А)</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -5565,12 +5409,12 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Динамический скроллер</t>
+          <t xml:space="preserve">Статичный плакат</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
@@ -5592,12 +5436,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S20</t>
+          <t xml:space="preserve">S21</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Марко Сити_2 (ул. Ленина, 26А)</t>
+          <t xml:space="preserve">Марко Сити_3 (ул. Ленина, 26А)</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -5644,12 +5488,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S20</t>
+          <t xml:space="preserve">S21</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Марко Сити_2 (ул. Ленина, 26А)</t>
+          <t xml:space="preserve">Марко Сити_3 (ул. Ленина, 26А)</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -5669,12 +5513,12 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Статичный плакат</t>
+          <t xml:space="preserve">Динамический скроллер</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr">
@@ -5696,12 +5540,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S21</t>
+          <t xml:space="preserve">S22</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Марко Сити_3 (ул. Ленина, 26А)</t>
+          <t xml:space="preserve">Марко Сити_4 (ул. Ленина, 26А)</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -5748,12 +5592,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S21</t>
+          <t xml:space="preserve">S22</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Марко Сити_3 (ул. Ленина, 26А)</t>
+          <t xml:space="preserve">Марко Сити_4 (ул. Ленина, 26А)</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -5800,12 +5644,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S22</t>
+          <t xml:space="preserve">S23</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Марко Сити_4 (ул. Ленина, 26А)</t>
+          <t xml:space="preserve">Марко Сити_5 (ул. Калинина, 2)</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -5852,12 +5696,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S22</t>
+          <t xml:space="preserve">S23</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Марко Сити_4 (ул. Ленина, 26А)</t>
+          <t xml:space="preserve">Марко Сити_5 (ул. Калинина, 2)</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -5882,7 +5726,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr">
@@ -5904,12 +5748,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S23</t>
+          <t xml:space="preserve">S24</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Марко Сити_5 (ул. Калинина, 2)</t>
+          <t xml:space="preserve">ул. Ленина, 28 «Синий» дом</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -5929,12 +5773,12 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Динамический скроллер</t>
+          <t xml:space="preserve">Медиа-скроллер</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
@@ -5956,12 +5800,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S23</t>
+          <t xml:space="preserve">S24</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Марко Сити_5 (ул. Калинина, 2)</t>
+          <t xml:space="preserve">ул. Ленина, 28 «Синий» дом</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -5981,12 +5825,12 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Динамический скроллер</t>
+          <t xml:space="preserve">Медиа-скроллер</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr">
@@ -6008,12 +5852,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S24</t>
+          <t xml:space="preserve">S25</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ул. Ленина, 28 «Синий» дом</t>
+          <t xml:space="preserve">ул. Ленина, 35, ТЦ «Пассаж»</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -6033,12 +5877,12 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Медиа-скроллер</t>
+          <t xml:space="preserve">Статичный плакат</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr">
@@ -6060,12 +5904,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S24</t>
+          <t xml:space="preserve">S25</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ул. Ленина, 28 «Синий» дом</t>
+          <t xml:space="preserve">ул. Ленина, 35, ТЦ «Пассаж»</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -6085,12 +5929,12 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Медиа-скроллер</t>
+          <t xml:space="preserve">Статичный плакат</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr">
@@ -6112,12 +5956,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S25</t>
+          <t xml:space="preserve">S26</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ул. Ленина, 35, ТЦ «Пассаж»</t>
+          <t xml:space="preserve">ул. Ленина, 53 (Белла Мария)</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -6164,12 +6008,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S25</t>
+          <t xml:space="preserve">S26</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ул. Ленина, 35, ТЦ «Пассаж»</t>
+          <t xml:space="preserve">ул. Ленина, 53 (Белла Мария)</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -6216,12 +6060,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S26</t>
+          <t xml:space="preserve">S27</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ул. Ленина, 53 (Белла Мария)</t>
+          <t xml:space="preserve">Пересечение ул. Коммунистической и ул. Горовца</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -6268,12 +6112,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S26</t>
+          <t xml:space="preserve">S27</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ул. Ленина, 53 (Белла Мария)</t>
+          <t xml:space="preserve">Пересечение ул. Коммунистической и ул. Горовца</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -6320,12 +6164,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S27</t>
+          <t xml:space="preserve">S28</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Пересечение ул. Коммунистической и ул. Горовца</t>
+          <t xml:space="preserve">пр-т Московский, 9, к. 1</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -6340,7 +6184,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">По ходу движения потока</t>
+          <t xml:space="preserve">По ходу движения транспорта</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -6372,12 +6216,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S27</t>
+          <t xml:space="preserve">S28</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Пересечение ул. Коммунистической и ул. Горовца</t>
+          <t xml:space="preserve">пр-т Московский, 9, к. 1</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -6392,7 +6236,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Против хода движения потока</t>
+          <t xml:space="preserve">Против хода движения транспорта</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -6424,12 +6268,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S28</t>
+          <t xml:space="preserve">S29</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">пр-т Московский, 9, к. 1</t>
+          <t xml:space="preserve">Московский пр-т, 10 (Почта)</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -6449,12 +6293,12 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Статичный плакат</t>
+          <t xml:space="preserve">Медиа-скроллер</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr">
@@ -6476,12 +6320,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S28</t>
+          <t xml:space="preserve">S29</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">пр-т Московский, 9, к. 1</t>
+          <t xml:space="preserve">Московский пр-т, 10 (Почта)</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -6501,7 +6345,7 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Статичный плакат</t>
+          <t xml:space="preserve">Динамический скроллер</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -6528,12 +6372,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S29</t>
+          <t xml:space="preserve">S30</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Московский пр-т, 10 (Почта)</t>
+          <t xml:space="preserve">Московский пр-т, 16</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -6553,12 +6397,12 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Медиа-скроллер</t>
+          <t xml:space="preserve">Динамический скроллер</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr">
@@ -6580,12 +6424,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S29</t>
+          <t xml:space="preserve">S30</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Московский пр-т, 10 (Почта)</t>
+          <t xml:space="preserve">Московский пр-т, 16</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -6605,7 +6449,7 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Динамический скроллер</t>
+          <t xml:space="preserve">Статичный плакат</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -6632,12 +6476,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S30</t>
+          <t xml:space="preserve">S31</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Московский пр-т, 16</t>
+          <t xml:space="preserve">пр-т Московский, 17/1 (школа № 31)</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -6657,7 +6501,7 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Динамический скроллер</t>
+          <t xml:space="preserve">Статичный плакат</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -6684,12 +6528,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S30</t>
+          <t xml:space="preserve">S31</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Московский пр-т, 16</t>
+          <t xml:space="preserve">пр-т Московский, 17/1 (школа № 31)</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -6736,12 +6580,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S31</t>
+          <t xml:space="preserve">S32</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">пр-т Московский, 17/1 (школа № 31)</t>
+          <t xml:space="preserve">Московский пр-т, 30 (м-н «Витебские продукты»)</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -6761,7 +6605,7 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Статичный плакат</t>
+          <t xml:space="preserve">Динамический скроллер</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -6788,12 +6632,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S31</t>
+          <t xml:space="preserve">S32</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">пр-т Московский, 17/1 (школа № 31)</t>
+          <t xml:space="preserve">Московский пр-т, 30 (м-н «Витебские продукты»)</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -6813,7 +6657,7 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Статичный плакат</t>
+          <t xml:space="preserve">Динамический скроллер</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -6840,12 +6684,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S32</t>
+          <t xml:space="preserve">S33</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Московский пр-т, 30 (м-н «Витебские продукты»)</t>
+          <t xml:space="preserve">Победы пр-т / Московский пр-т, 33 (Педуниверситет)</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -6865,7 +6709,7 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Динамический скроллер</t>
+          <t xml:space="preserve">Статичный плакат</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -6892,12 +6736,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S32</t>
+          <t xml:space="preserve">S33</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Московский пр-т, 30 (м-н «Витебские продукты»)</t>
+          <t xml:space="preserve">Победы пр-т / Московский пр-т, 33 (Педуниверситет)</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -6917,7 +6761,7 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Динамический скроллер</t>
+          <t xml:space="preserve">Статичный плакат</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -6944,12 +6788,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S33</t>
+          <t xml:space="preserve">S34</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Победы пр-т / Московский пр-т, 33 (Педуниверситет)</t>
+          <t xml:space="preserve">Московский пр-т, 35 (м-н «Астраханский»)</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -6969,7 +6813,7 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Статичный плакат</t>
+          <t xml:space="preserve">Динамический скроллер</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -6996,12 +6840,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S33</t>
+          <t xml:space="preserve">S34</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Победы пр-т / Московский пр-т, 33 (Педуниверситет)</t>
+          <t xml:space="preserve">Московский пр-т, 35 (м-н «Астраханский»)</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -7048,12 +6892,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S34</t>
+          <t xml:space="preserve">S35</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Московский пр-т, 35 (м-н «Астраханский»)</t>
+          <t xml:space="preserve">Московский пр-т, 60 (м-н «Евроопт»)</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -7078,7 +6922,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr">
@@ -7100,12 +6944,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S34</t>
+          <t xml:space="preserve">S35</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Московский пр-т, 35 (м-н «Астраханский»)</t>
+          <t xml:space="preserve">Московский пр-т, 60 (м-н «Евроопт»)</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -7125,7 +6969,7 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Статичный плакат</t>
+          <t xml:space="preserve">Динамический скроллер</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -7152,12 +6996,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S35</t>
+          <t xml:space="preserve">S36</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Московский пр-т, 60 (м-н «Евроопт»)</t>
+          <t xml:space="preserve">Московский пр-т, 68 (перекрёсток Машерова)</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -7177,12 +7021,12 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Динамический скроллер</t>
+          <t xml:space="preserve">Статичный плакат</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr">
@@ -7204,12 +7048,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S35</t>
+          <t xml:space="preserve">S36</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Московский пр-т, 60 (м-н «Евроопт»)</t>
+          <t xml:space="preserve">Московский пр-т, 68 (перекрёсток Машерова)</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -7229,7 +7073,7 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Динамический скроллер</t>
+          <t xml:space="preserve">Статичный плакат</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -7256,12 +7100,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S36</t>
+          <t xml:space="preserve">S37</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Московский пр-т, 68 (перекрёсток Машерова)</t>
+          <t xml:space="preserve">Московский пр-т, 86 (МакДональдс)</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -7281,7 +7125,7 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Статичный плакат</t>
+          <t xml:space="preserve">Динамический скроллер</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -7308,12 +7152,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S36</t>
+          <t xml:space="preserve">S37</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Московский пр-т, 68 (перекрёсток Машерова)</t>
+          <t xml:space="preserve">Московский пр-т, 86 (МакДональдс)</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -7333,7 +7177,7 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Статичный плакат</t>
+          <t xml:space="preserve">Динамический скроллер</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -7360,12 +7204,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S37</t>
+          <t xml:space="preserve">S38</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Московский пр-т, 86 (МакДональдс)</t>
+          <t xml:space="preserve">Перекрёсток пр-та Строителей и пр-та Черняховского</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -7385,7 +7229,7 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Динамический скроллер</t>
+          <t xml:space="preserve">Статичный плакат</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -7412,12 +7256,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S37</t>
+          <t xml:space="preserve">S38</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Московский пр-т, 86 (МакДональдс)</t>
+          <t xml:space="preserve">Перекрёсток пр-та Строителей и пр-та Черняховского</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -7437,7 +7281,7 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Динамический скроллер</t>
+          <t xml:space="preserve">Статичный плакат</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -7464,12 +7308,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S38</t>
+          <t xml:space="preserve">S39</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Перекрёсток пр-та Строителей и пр-та Черняховского</t>
+          <t xml:space="preserve">Строителей пр-т, 1 (Континент-1)</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -7484,17 +7328,17 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">По ходу движения транспорта</t>
+          <t xml:space="preserve">По ходу движения потока</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Статичный плакат</t>
+          <t xml:space="preserve">Динамический скроллер</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr">
@@ -7516,12 +7360,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S38</t>
+          <t xml:space="preserve">S39</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Перекрёсток пр-та Строителей и пр-та Черняховского</t>
+          <t xml:space="preserve">Строителей пр-т, 1 (Континент-1)</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -7536,12 +7380,12 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Против хода движения транспорта</t>
+          <t xml:space="preserve">Против хода движения потока</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Статичный плакат</t>
+          <t xml:space="preserve">Динамический скроллер</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -7568,12 +7412,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S39</t>
+          <t xml:space="preserve">S40</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Строителей пр-т, 1 (Континент-1)</t>
+          <t xml:space="preserve">Строителей пр-т, 1 (Континент-2)</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -7620,12 +7464,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S39</t>
+          <t xml:space="preserve">S40</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Строителей пр-т, 1 (Континент-1)</t>
+          <t xml:space="preserve">Строителей пр-т, 1 (Континент-2)</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -7672,12 +7516,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S40</t>
+          <t xml:space="preserve">S41</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Строителей пр-т, 1 (Континент-2)</t>
+          <t xml:space="preserve">Строителей пр-т, 8к2 — ул. Чкалова (офис МТС)</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -7697,12 +7541,12 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Динамический скроллер</t>
+          <t xml:space="preserve">Статичный плакат</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr">
@@ -7724,12 +7568,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S40</t>
+          <t xml:space="preserve">S41</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Строителей пр-т, 1 (Континент-2)</t>
+          <t xml:space="preserve">Строителей пр-т, 8к2 — ул. Чкалова (офис МТС)</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -7749,7 +7593,7 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Динамический скроллер</t>
+          <t xml:space="preserve">Статичный плакат</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -7776,12 +7620,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S41</t>
+          <t xml:space="preserve">S42</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Строителей пр-т, 8к2 — ул. Чкалова (офис МТС)</t>
+          <t xml:space="preserve">Строителей пр-т, 9 «Бригантина»</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -7828,12 +7672,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S41</t>
+          <t xml:space="preserve">S42</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Строителей пр-т, 8к2 — ул. Чкалова (офис МТС)</t>
+          <t xml:space="preserve">Строителей пр-т, 9 «Бригантина»</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -7880,12 +7724,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S42</t>
+          <t xml:space="preserve">S43</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Строителей пр-т, 9 «Бригантина»</t>
+          <t xml:space="preserve">Строителей пр-т, 15В (ТЦ «ТРИО»)</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -7905,12 +7749,12 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Статичный плакат</t>
+          <t xml:space="preserve">Медиа-скроллер</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H84" s="4" t="inlineStr">
@@ -7932,12 +7776,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S42</t>
+          <t xml:space="preserve">S43</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Строителей пр-т, 9 «Бригантина»</t>
+          <t xml:space="preserve">Строителей пр-т, 15В (ТЦ «ТРИО»)</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -7957,12 +7801,12 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Статичный плакат</t>
+          <t xml:space="preserve">Динамический скроллер</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H85" s="4" t="inlineStr">
@@ -7984,12 +7828,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S43</t>
+          <t xml:space="preserve">S44</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Строителей пр-т, 15В (ТЦ «ТРИО»)</t>
+          <t xml:space="preserve">Строителей пр-т, 15В (ТЦ «ТРИО-2»)</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -8009,12 +7853,12 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Медиа-скроллер</t>
+          <t xml:space="preserve">Динамический скроллер</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H86" s="4" t="inlineStr">
@@ -8036,12 +7880,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S43</t>
+          <t xml:space="preserve">S44</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Строителей пр-т, 15В (ТЦ «ТРИО»)</t>
+          <t xml:space="preserve">Строителей пр-т, 15В (ТЦ «ТРИО-2»)</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -8088,12 +7932,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S44</t>
+          <t xml:space="preserve">S45</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Строителей пр-т, 15В (ТЦ «ТРИО-2»)</t>
+          <t xml:space="preserve">Черняховского пр-т, 3</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -8108,7 +7952,7 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">По ходу движения потока</t>
+          <t xml:space="preserve">По ходу движения транспорта</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
@@ -8118,7 +7962,7 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H88" s="4" t="inlineStr">
@@ -8140,12 +7984,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S44</t>
+          <t xml:space="preserve">S45</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Строителей пр-т, 15В (ТЦ «ТРИО-2»)</t>
+          <t xml:space="preserve">Черняховского пр-т, 3</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -8160,17 +8004,17 @@
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Против хода движения потока</t>
+          <t xml:space="preserve">Против хода движения транспорта</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Динамический скроллер</t>
+          <t xml:space="preserve">Статичный плакат</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H89" s="4" t="inlineStr">
@@ -8192,12 +8036,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S45</t>
+          <t xml:space="preserve">S46</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Черняховского пр-т, 3</t>
+          <t xml:space="preserve">ул. Чкалова (ТД «Омега»)</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -8212,17 +8056,17 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">По ходу движения транспорта</t>
+          <t xml:space="preserve">По ходу движения потока</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Динамический скроллер</t>
+          <t xml:space="preserve">Статичный плакат</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H90" s="4" t="inlineStr">
@@ -8244,12 +8088,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S45</t>
+          <t xml:space="preserve">S46</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Черняховского пр-т, 3</t>
+          <t xml:space="preserve">ул. Чкалова (ТД «Омега»)</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -8264,7 +8108,7 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Против хода движения транспорта</t>
+          <t xml:space="preserve">Против хода движения потока</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
@@ -8296,12 +8140,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S46</t>
+          <t xml:space="preserve">S47</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ул. Чкалова (ТД «Омега»)</t>
+          <t xml:space="preserve">пр-т Фрунзе, 16</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -8348,12 +8192,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S46</t>
+          <t xml:space="preserve">S47</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ул. Чкалова (ТД «Омега»)</t>
+          <t xml:space="preserve">пр-т Фрунзе, 16</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -8400,12 +8244,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S47</t>
+          <t xml:space="preserve">S48</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">пр-т Фрунзе, 16</t>
+          <t xml:space="preserve">ул. Фрунзе, 46 («Зелена Гура»)</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -8425,12 +8269,12 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Статичный плакат</t>
+          <t xml:space="preserve">Динамический скроллер</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H94" s="4" t="inlineStr">
@@ -8452,12 +8296,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S47</t>
+          <t xml:space="preserve">S48</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">пр-т Фрунзе, 16</t>
+          <t xml:space="preserve">ул. Фрунзе, 46 («Зелена Гура»)</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -8477,7 +8321,7 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Статичный плакат</t>
+          <t xml:space="preserve">Динамический скроллер</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
@@ -8504,12 +8348,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S48</t>
+          <t xml:space="preserve">S49</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ул. Фрунзе, 46 («Зелена Гура»)</t>
+          <t xml:space="preserve">Перекрёсток пр-та Фрунзе и ул. Смоленской</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -8524,17 +8368,17 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">По ходу движения потока</t>
+          <t xml:space="preserve">По ходу движения транспорта</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Динамический скроллер</t>
+          <t xml:space="preserve">Статичный плакат</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H96" s="4" t="inlineStr">
@@ -8556,12 +8400,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S48</t>
+          <t xml:space="preserve">S49</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ул. Фрунзе, 46 («Зелена Гура»)</t>
+          <t xml:space="preserve">Перекрёсток пр-та Фрунзе и ул. Смоленской</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -8576,12 +8420,12 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Против хода движения потока</t>
+          <t xml:space="preserve">Против хода движения транспорта</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Динамический скроллер</t>
+          <t xml:space="preserve">Статичный плакат</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
@@ -8608,17 +8452,17 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S49</t>
+          <t xml:space="preserve">S50</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Перекрёсток пр-та Фрунзе и ул. Смоленской</t>
+          <t xml:space="preserve">г. Полоцк, ул. Гоголя (Дом торговли)</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Витебск</t>
+          <t xml:space="preserve">Полоцк</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
@@ -8628,7 +8472,7 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">По ходу движения транспорта</t>
+          <t xml:space="preserve">По ходу движения потока</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
@@ -8660,17 +8504,17 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S49</t>
+          <t xml:space="preserve">S50</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Перекрёсток пр-та Фрунзе и ул. Смоленской</t>
+          <t xml:space="preserve">г. Полоцк, ул. Гоголя (Дом торговли)</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Витебск</t>
+          <t xml:space="preserve">Полоцк</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
@@ -8680,7 +8524,7 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Против хода движения транспорта</t>
+          <t xml:space="preserve">Против хода движения потока</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
@@ -8712,12 +8556,12 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S50</t>
+          <t xml:space="preserve">S51</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">г. Полоцк, ул. Гоголя (Дом торговли)</t>
+          <t xml:space="preserve">г. Полоцк, ул. Октябрьская (ТЦ «Дионис»)</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -8764,12 +8608,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S50</t>
+          <t xml:space="preserve">S51</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">г. Полоцк, ул. Гоголя (Дом торговли)</t>
+          <t xml:space="preserve">г. Полоцк, ул. Октябрьская (ТЦ «Дионис»)</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -8816,12 +8660,12 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S51</t>
+          <t xml:space="preserve">S52</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">г. Полоцк, ул. Октябрьская (ТЦ «Дионис»)</t>
+          <t xml:space="preserve">г. Полоцк, ул. Юбилейная, д. 7Б</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -8868,12 +8712,12 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S51</t>
+          <t xml:space="preserve">S52</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">г. Полоцк, ул. Октябрьская (ТЦ «Дионис»)</t>
+          <t xml:space="preserve">г. Полоцк, ул. Юбилейная, д. 7Б</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -8920,212 +8764,108 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S52</t>
+          <t xml:space="preserve">LED-1</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">г. Полоцк, ул. Юбилейная, д. 7Б</t>
+          <t xml:space="preserve">LED-экран 6×3, Ленина 26А (ТЦ «Марко-Сити»)</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Полоцк</t>
+          <t xml:space="preserve">Витебск</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">По ходу движения потока</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Статичный плакат</t>
+          <t xml:space="preserve">LED-экран 6×3</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="H104" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">нужно снять</t>
+        </is>
+      </c>
+      <c r="I104" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">нужно снять</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">2</t>
-        </is>
-      </c>
-      <c r="H104" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">есть</t>
-        </is>
-      </c>
-      <c r="I104" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">нужно снять</t>
-        </is>
-      </c>
-      <c r="J104" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S52</t>
+          <t xml:space="preserve">LED-2</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">г. Полоцк, ул. Юбилейная, д. 7Б</t>
+          <t xml:space="preserve">LED-экран 6×3, Московский 60 (Евроопт)</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Полоцк</t>
+          <t xml:space="preserve">Витебск</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">B</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Против хода движения потока</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Статичный плакат</t>
+          <t xml:space="preserve">LED-экран 6×3</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="H105" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">нужно снять</t>
+        </is>
+      </c>
+      <c r="I105" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">нужно снять</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="H105" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">есть</t>
-        </is>
-      </c>
-      <c r="I105" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">нужно снять</t>
-        </is>
-      </c>
-      <c r="J105" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LED-1</t>
-        </is>
-      </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LED-экран 6×3, Ленина 26А (ТЦ «Марко-Сити»)</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Витебск</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="E106" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="F106" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LED-экран 6×3</t>
-        </is>
-      </c>
-      <c r="G106" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="H106" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">нужно снять</t>
-        </is>
-      </c>
-      <c r="I106" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">нужно снять</t>
-        </is>
-      </c>
-      <c r="J106" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LED-2</t>
-        </is>
-      </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LED-экран 6×3, Московский 60 (Евроопт)</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Витебск</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="E107" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="F107" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LED-экран 6×3</t>
-        </is>
-      </c>
-      <c r="G107" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="H107" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">нужно снять</t>
-        </is>
-      </c>
-      <c r="I107" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">нужно снять</t>
-        </is>
-      </c>
-      <c r="J107" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2</t>
-        </is>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J107"/>
+  <autoFilter ref="A1:J105"/>
 </worksheet>
 </file>